--- a/research/traditional_assets/database/data/australia/australia_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_publishing_newspapers.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.08019999999999999</v>
+        <v>-0.0156</v>
       </c>
       <c r="G2">
-        <v>-0.009996127337792232</v>
+        <v>0.02717391304347826</v>
       </c>
       <c r="H2">
-        <v>-0.009996127337792232</v>
+        <v>0.02717391304347826</v>
       </c>
       <c r="I2">
-        <v>-0.05306711935079041</v>
+        <v>-0.04257246376811594</v>
       </c>
       <c r="J2">
-        <v>-0.05306711935079041</v>
+        <v>-0.04257246376811594</v>
       </c>
       <c r="K2">
-        <v>-52.611</v>
+        <v>-1.127</v>
       </c>
       <c r="L2">
-        <v>-0.1531914521900924</v>
+        <v>-0.0928030303030303</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>22.234</v>
+        <v>4.556999999999999</v>
       </c>
       <c r="V2">
-        <v>0.2722086190009795</v>
+        <v>0.1430320150659134</v>
       </c>
       <c r="W2">
-        <v>-2.026904288356188</v>
+        <v>1.011166822601405</v>
       </c>
       <c r="X2">
-        <v>0.05635602008842104</v>
+        <v>0.09038770782066349</v>
       </c>
       <c r="Y2">
-        <v>-2.083260308444609</v>
+        <v>0.9207791147807415</v>
       </c>
       <c r="Z2">
-        <v>2.546721244614506</v>
-      </c>
-      <c r="AA2">
-        <v>-0.1036071487746464</v>
+        <v>282.418604651156</v>
       </c>
       <c r="AB2">
-        <v>0.05230320149883808</v>
-      </c>
-      <c r="AC2">
-        <v>-0.156009561609615</v>
+        <v>0.09037171635293059</v>
       </c>
       <c r="AD2">
-        <v>101.968</v>
+        <v>0.023</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>101.968</v>
+        <v>0.023</v>
       </c>
       <c r="AG2">
-        <v>79.73400000000001</v>
+        <v>-4.534</v>
       </c>
       <c r="AH2">
-        <v>0.5552361038508451</v>
+        <v>0.0007213875733149327</v>
       </c>
       <c r="AI2">
-        <v>0.8891601775390438</v>
+        <v>0.005128205128205129</v>
       </c>
       <c r="AJ2">
-        <v>0.4939720222533363</v>
+        <v>-0.1659225645904999</v>
       </c>
       <c r="AK2">
-        <v>0.8625020282330035</v>
+        <v>62.97222222222216</v>
       </c>
       <c r="AL2">
-        <v>11.975</v>
+        <v>0.008</v>
       </c>
       <c r="AM2">
-        <v>11.952</v>
+        <v>-0.008</v>
       </c>
       <c r="AN2">
-        <v>-29.70230119429071</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="AO2">
-        <v>-1.521920668058455</v>
+        <v>-64.62499999999999</v>
       </c>
       <c r="AP2">
-        <v>-23.22575007282261</v>
+        <v>-13.73939393939394</v>
       </c>
       <c r="AQ2">
-        <v>-1.524849397590361</v>
+        <v>64.62499999999999</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>333D Limited (ASX:T3D)</t>
+          <t>Aspermont Limited (ASX:ASP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0444</v>
+        <v>0.0968</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.02727272727272727</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.02727272727272727</v>
       </c>
       <c r="I3">
-        <v>-2.174418604651163</v>
+        <v>0.02727272727272727</v>
       </c>
       <c r="J3">
-        <v>-2.174418604651163</v>
+        <v>0.02727272727272727</v>
       </c>
       <c r="K3">
-        <v>-0.254</v>
+        <v>-0.276</v>
       </c>
       <c r="L3">
-        <v>-2.953488372093024</v>
+        <v>-0.0228099173553719</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,67 +752,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.074</v>
+        <v>4.27</v>
       </c>
       <c r="V3">
-        <v>0.01813725490196078</v>
+        <v>0.1437710437710438</v>
       </c>
       <c r="W3">
-        <v>0.1558282208588957</v>
+        <v>-0.05835095137420719</v>
       </c>
       <c r="X3">
-        <v>0.05418109238745954</v>
+        <v>0.09040168655868083</v>
       </c>
       <c r="Y3">
-        <v>0.1016471284714362</v>
+        <v>-0.148752637932888</v>
       </c>
       <c r="Z3">
-        <v>-0.1170068027210884</v>
+        <v>281.3953488372025</v>
       </c>
       <c r="AA3">
-        <v>0.254421768707483</v>
+        <v>7.674418604650978</v>
       </c>
       <c r="AB3">
-        <v>0.05248386424682912</v>
+        <v>0.09036970362321504</v>
       </c>
       <c r="AC3">
-        <v>0.2019379044606539</v>
+        <v>7.584048901027764</v>
       </c>
       <c r="AD3">
-        <v>0.225</v>
+        <v>0.023</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.225</v>
+        <v>0.023</v>
       </c>
       <c r="AG3">
-        <v>0.151</v>
+        <v>-4.247</v>
       </c>
       <c r="AH3">
-        <v>0.05226480836236935</v>
+        <v>0.0007738115264273458</v>
       </c>
       <c r="AI3">
-        <v>-1.222826086956522</v>
+        <v>0.005188360027069704</v>
       </c>
       <c r="AJ3">
-        <v>0.03568896242023163</v>
+        <v>-0.166856559148234</v>
       </c>
       <c r="AK3">
-        <v>-0.5852713178294575</v>
+        <v>-26.05521472392634</v>
       </c>
       <c r="AL3">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.092</v>
-      </c>
-      <c r="AO3">
-        <v>-2.032608695652174</v>
+        <v>-0.016</v>
+      </c>
+      <c r="AN3">
+        <v>0.06969696969696969</v>
+      </c>
+      <c r="AP3">
+        <v>-12.86969696969697</v>
       </c>
       <c r="AQ3">
-        <v>-2.032608695652174</v>
+        <v>-20.625</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aspermont Limited (ASX:ASP)</t>
+          <t>333D Limited (ASX:T3D)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,23 +834,26 @@
           <t>Publishing &amp; Newspapers</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.128</v>
+      </c>
       <c r="G4">
-        <v>-0.002844827586206897</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>-0.002844827586206897</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.005862068965517242</v>
+        <v>-19.25</v>
       </c>
       <c r="J4">
-        <v>-0.005862068965517242</v>
+        <v>-19.25</v>
       </c>
       <c r="K4">
-        <v>0.083</v>
+        <v>-0.851</v>
       </c>
       <c r="L4">
-        <v>0.007155172413793104</v>
+        <v>-19.34090909090909</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -862,7 +862,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -871,308 +871,64 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.09</v>
+        <v>0.287</v>
       </c>
       <c r="V4">
-        <v>0.125990099009901</v>
+        <v>0.1328703703703704</v>
       </c>
       <c r="W4">
-        <v>0.03562231759656653</v>
+        <v>2.080684596577017</v>
       </c>
       <c r="X4">
-        <v>0.05299126847835942</v>
+        <v>0.09037372908264614</v>
       </c>
       <c r="Y4">
-        <v>-0.01736895088179289</v>
-      </c>
-      <c r="Z4">
-        <v>14.72081218274111</v>
-      </c>
-      <c r="AA4">
-        <v>-0.0862944162436548</v>
+        <v>1.990310867494371</v>
       </c>
       <c r="AB4">
-        <v>0.05268228691909017</v>
-      </c>
-      <c r="AC4">
-        <v>-0.138976703162745</v>
+        <v>0.09037372908264614</v>
       </c>
       <c r="AD4">
-        <v>0.403</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.403</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-4.686999999999999</v>
+        <v>-0.287</v>
       </c>
       <c r="AH4">
-        <v>0.009876724750631082</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.07851159166179621</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.131240724666088</v>
+        <v>-0.1532301121195942</v>
       </c>
       <c r="AK4">
-        <v>-108.9999999999974</v>
+        <v>1.221276595744681</v>
       </c>
       <c r="AL4">
-        <v>0.083</v>
+        <v>0.008</v>
       </c>
       <c r="AM4">
-        <v>0.083</v>
-      </c>
-      <c r="AN4">
-        <v>-12.21212121212121</v>
+        <v>0.008</v>
       </c>
       <c r="AO4">
-        <v>-0.8192771084337349</v>
-      </c>
-      <c r="AP4">
-        <v>142.030303030303</v>
+        <v>-105.875</v>
       </c>
       <c r="AQ4">
-        <v>-0.8192771084337349</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ovato Limited (ASX:OVT)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Publishing &amp; Newspapers</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.116</v>
-      </c>
-      <c r="G5">
-        <v>-0.01024404941247364</v>
-      </c>
-      <c r="H5">
-        <v>-0.01024404941247364</v>
-      </c>
-      <c r="I5">
-        <v>-0.04911117806568244</v>
-      </c>
-      <c r="J5">
-        <v>-0.04911117806568244</v>
-      </c>
-      <c r="K5">
-        <v>-50.3</v>
-      </c>
-      <c r="L5">
-        <v>-0.1515516721904188</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>12.5</v>
-      </c>
-      <c r="V5">
-        <v>0.5341880341880342</v>
-      </c>
-      <c r="W5">
-        <v>-4.089430894308943</v>
-      </c>
-      <c r="X5">
-        <v>0.1633788847894953</v>
-      </c>
-      <c r="Y5">
-        <v>-4.252809779098438</v>
-      </c>
-      <c r="Z5">
-        <v>2.462166172106825</v>
-      </c>
-      <c r="AA5">
-        <v>-0.120919881305638</v>
-      </c>
-      <c r="AB5">
-        <v>0.05212253875084703</v>
-      </c>
-      <c r="AC5">
-        <v>-0.173042420056485</v>
-      </c>
-      <c r="AD5">
-        <v>98.3</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>98.3</v>
-      </c>
-      <c r="AG5">
-        <v>85.8</v>
-      </c>
-      <c r="AH5">
-        <v>0.8077239112571899</v>
-      </c>
-      <c r="AI5">
-        <v>0.9461020211742061</v>
-      </c>
-      <c r="AJ5">
-        <v>0.7857142857142858</v>
-      </c>
-      <c r="AK5">
-        <v>0.9387308533916849</v>
-      </c>
-      <c r="AL5">
-        <v>11.8</v>
-      </c>
-      <c r="AM5">
-        <v>11.791</v>
-      </c>
-      <c r="AN5">
-        <v>-28.91176470588235</v>
-      </c>
-      <c r="AO5">
-        <v>-1.38135593220339</v>
-      </c>
-      <c r="AP5">
-        <v>-25.23529411764706</v>
-      </c>
-      <c r="AQ5">
-        <v>-1.382410312950556</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3D Metalforge Limited (ASX:3MF)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Publishing &amp; Newspapers</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>-0</v>
-      </c>
-      <c r="H6">
-        <v>-0</v>
-      </c>
-      <c r="I6">
-        <v>10.91503267973856</v>
-      </c>
-      <c r="J6">
-        <v>10.91503267973856</v>
-      </c>
-      <c r="K6">
-        <v>-2.14</v>
-      </c>
-      <c r="L6">
-        <v>13.98692810457517</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>4.57</v>
-      </c>
-      <c r="V6">
-        <v>0.3311594202898551</v>
-      </c>
-      <c r="X6">
-        <v>0.05853094778938255</v>
-      </c>
-      <c r="AB6">
-        <v>0.05188347742332985</v>
-      </c>
-      <c r="AD6">
-        <v>3.04</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>3.04</v>
-      </c>
-      <c r="AG6">
-        <v>-1.53</v>
-      </c>
-      <c r="AH6">
-        <v>0.1805225653206651</v>
-      </c>
-      <c r="AI6">
-        <v>0.5214408233276158</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.1246943765281174</v>
-      </c>
-      <c r="AK6">
-        <v>-1.214285714285715</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>-0.014</v>
-      </c>
-      <c r="AQ6">
-        <v>119.2857142857143</v>
+        <v>-105.875</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_publishing_newspapers.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0156</v>
+        <v>0.0653</v>
       </c>
       <c r="G2">
-        <v>0.02717391304347826</v>
+        <v>0.002419354838709677</v>
       </c>
       <c r="H2">
-        <v>0.02717391304347826</v>
+        <v>0.002419354838709677</v>
       </c>
       <c r="I2">
-        <v>-0.04257246376811594</v>
+        <v>-0.03588709677419355</v>
       </c>
       <c r="J2">
-        <v>-0.04257246376811594</v>
+        <v>-0.03588709677419355</v>
       </c>
       <c r="K2">
-        <v>-1.127</v>
+        <v>-1.1</v>
       </c>
       <c r="L2">
-        <v>-0.0928030303030303</v>
+        <v>-0.08870967741935484</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.556999999999999</v>
+        <v>2.61</v>
       </c>
       <c r="V2">
-        <v>0.1430320150659134</v>
+        <v>0.1751677852348993</v>
       </c>
       <c r="W2">
-        <v>1.011166822601405</v>
+        <v>-0.2494331065759637</v>
       </c>
       <c r="X2">
-        <v>0.09038770782066349</v>
+        <v>0.08454788972042192</v>
       </c>
       <c r="Y2">
-        <v>0.9207791147807415</v>
+        <v>-0.3339809962963857</v>
       </c>
       <c r="Z2">
-        <v>282.418604651156</v>
+        <v>76.07361963190172</v>
+      </c>
+      <c r="AA2">
+        <v>-2.730061349693247</v>
       </c>
       <c r="AB2">
-        <v>0.09037171635293059</v>
+        <v>0.083558011355735</v>
+      </c>
+      <c r="AC2">
+        <v>-2.813619361048982</v>
       </c>
       <c r="AD2">
-        <v>0.023</v>
+        <v>0.32</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.023</v>
+        <v>0.32</v>
       </c>
       <c r="AG2">
-        <v>-4.534</v>
+        <v>-2.29</v>
       </c>
       <c r="AH2">
-        <v>0.0007213875733149327</v>
+        <v>0.02102496714848883</v>
       </c>
       <c r="AI2">
-        <v>0.005128205128205129</v>
+        <v>0.09609609609609611</v>
       </c>
       <c r="AJ2">
-        <v>-0.1659225645904999</v>
+        <v>-0.1816019032513878</v>
       </c>
       <c r="AK2">
-        <v>62.97222222222216</v>
+        <v>-3.180555555555557</v>
       </c>
       <c r="AL2">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.008</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.06969696969696969</v>
-      </c>
-      <c r="AO2">
-        <v>-64.62499999999999</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="AP2">
-        <v>-13.73939393939394</v>
-      </c>
-      <c r="AQ2">
-        <v>64.62499999999999</v>
+        <v>-76.33333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0968</v>
+        <v>0.0653</v>
       </c>
       <c r="G3">
-        <v>0.02727272727272727</v>
+        <v>0.002419354838709677</v>
       </c>
       <c r="H3">
-        <v>0.02727272727272727</v>
+        <v>0.002419354838709677</v>
       </c>
       <c r="I3">
-        <v>0.02727272727272727</v>
+        <v>-0.03588709677419355</v>
       </c>
       <c r="J3">
-        <v>0.02727272727272727</v>
+        <v>-0.03588709677419355</v>
       </c>
       <c r="K3">
-        <v>-0.276</v>
+        <v>-1.1</v>
       </c>
       <c r="L3">
-        <v>-0.0228099173553719</v>
+        <v>-0.08870967741935484</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,183 +752,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.27</v>
+        <v>2.61</v>
       </c>
       <c r="V3">
-        <v>0.1437710437710438</v>
+        <v>0.1751677852348993</v>
       </c>
       <c r="W3">
-        <v>-0.05835095137420719</v>
+        <v>-0.2494331065759637</v>
       </c>
       <c r="X3">
-        <v>0.09040168655868083</v>
+        <v>0.08454788972042192</v>
       </c>
       <c r="Y3">
-        <v>-0.148752637932888</v>
+        <v>-0.3339809962963857</v>
       </c>
       <c r="Z3">
-        <v>281.3953488372025</v>
+        <v>76.07361963190172</v>
       </c>
       <c r="AA3">
-        <v>7.674418604650978</v>
+        <v>-2.730061349693247</v>
       </c>
       <c r="AB3">
-        <v>0.09036970362321504</v>
+        <v>0.083558011355735</v>
       </c>
       <c r="AC3">
-        <v>7.584048901027764</v>
+        <v>-2.813619361048982</v>
       </c>
       <c r="AD3">
-        <v>0.023</v>
+        <v>0.32</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.023</v>
+        <v>0.32</v>
       </c>
       <c r="AG3">
-        <v>-4.247</v>
+        <v>-2.29</v>
       </c>
       <c r="AH3">
-        <v>0.0007738115264273458</v>
+        <v>0.02102496714848883</v>
       </c>
       <c r="AI3">
-        <v>0.005188360027069704</v>
+        <v>0.09609609609609611</v>
       </c>
       <c r="AJ3">
-        <v>-0.166856559148234</v>
+        <v>-0.1816019032513878</v>
       </c>
       <c r="AK3">
-        <v>-26.05521472392634</v>
+        <v>-3.180555555555557</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.016</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.06969696969696969</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="AP3">
-        <v>-12.86969696969697</v>
-      </c>
-      <c r="AQ3">
-        <v>-20.625</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>333D Limited (ASX:T3D)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Publishing &amp; Newspapers</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.128</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>-19.25</v>
-      </c>
-      <c r="J4">
-        <v>-19.25</v>
-      </c>
-      <c r="K4">
-        <v>-0.851</v>
-      </c>
-      <c r="L4">
-        <v>-19.34090909090909</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.287</v>
-      </c>
-      <c r="V4">
-        <v>0.1328703703703704</v>
-      </c>
-      <c r="W4">
-        <v>2.080684596577017</v>
-      </c>
-      <c r="X4">
-        <v>0.09037372908264614</v>
-      </c>
-      <c r="Y4">
-        <v>1.990310867494371</v>
-      </c>
-      <c r="AB4">
-        <v>0.09037372908264614</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-0.287</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.1532301121195942</v>
-      </c>
-      <c r="AK4">
-        <v>1.221276595744681</v>
-      </c>
-      <c r="AL4">
-        <v>0.008</v>
-      </c>
-      <c r="AM4">
-        <v>0.008</v>
-      </c>
-      <c r="AO4">
-        <v>-105.875</v>
-      </c>
-      <c r="AQ4">
-        <v>-105.875</v>
+        <v>-76.33333333333334</v>
       </c>
     </row>
   </sheetData>
